--- a/calculations/design-master.xlsx
+++ b/calculations/design-master.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power budget" sheetId="1" r:id="Rd197f78ad24e4d37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LM61495 Main 5V" sheetId="2" r:id="R0d431532a5cc4315"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TPS62933F RF 5V" sheetId="3" r:id="Rc9a667a3d3db45b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TLV758 Camera 4V" sheetId="4" r:id="Rde8b782a0a3f4263"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TLV758 Camera 1V8" sheetId="5" r:id="R60c30f4539ab445c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Battery" sheetId="6" r:id="Re70c95fb57bd4f51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power budget" sheetId="1" r:id="R8cc0ac3eb68c4921"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LM61495 Main 5V" sheetId="2" r:id="R22e685437e944ea9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TPS62933F RF 5V" sheetId="3" r:id="Rc454dd2d70944e2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TLV758 Camera 4V" sheetId="4" r:id="R5108746e3d89496f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TLV758 Camera 1V8" sheetId="5" r:id="R508e59010a664e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Battery" sheetId="6" r:id="R3efef57a0db54424"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -74,6 +74,34 @@
       <x:text>
         <x:r>
           <x:t>TI SLVA477B equations 12–13: deltaV approximately deltaI [ESR + 1/(8 fs C)]. Nominal CCM estimate, not a transient/stability verification. https://www.ti.com/lit/an/slva477b/slva477b.pdf</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="B60" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>Texas Instruments LM61495 datasheet, sections 9.2.2.4 and 9.2.2.9, Table 9-3. https://www.ti.com/lit/gpn/lm61495 . CFF is a proposed frequency-scaled starting value for the 40k/10k divider. The full converter loop has not been modeled or measured.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="B80" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>Samsung CL32B106KBJNNNE typical DC-bias curve, 25 C, 1 kHz, 1 Vrms. 7.23962 uF at 12.6 V and 9.39267 uF at 5 V. These are typical curve values, not guaranteed minimum capacitance. https://product.samsungsem.com/mlcc/CL32B106KBJNNN.do</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="B92" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>SHOUHAN CYA1265-3.3UH manufacturer specification, 3R3M row: 3.3 uH +/-20%, DCR 5 mOhm typical / 6.5 mOhm maximum, thermal current 25 A at 40 C rise, Isat 45 A at 30% inductance loss. No current-bias or core-loss curve supplied. https://jlcpcb.com/partdetail/SHOUHAN-CYA1265_33UH/C19268665</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="B87" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>Texas Instruments LM61495, RT=VCC oscillator range 350-440 kHz. Equation 6: L &gt; Vout/(fsw*0.6*Irated). Spread-spectrum reduction is not included. https://www.ti.com/lit/gpn/lm61495</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -153,19 +181,37 @@
 </x:comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:authors>
+    <x:author/>
+  </x:authors>
+  <x:commentList>
+    <x:comment ref="B34" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>LM74502 nominal UVLO thresholds: falling 1.14 V, rising 1.24 V; OV rising 1.25 V. Divider equations here omit input bias and resistor/comparator tolerance. https://www.ti.com/lit/gpn/lm74502 . Resistors and capacitor values from saved carrier schematic.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+  </x:commentList>
+</x:comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="200" formatCode="0.0"/>
     <x:numFmt numFmtId="201" formatCode="0.000"/>
     <x:numFmt numFmtId="202" formatCode="0.00"/>
     <x:numFmt numFmtId="203" formatCode="0%"/>
     <x:numFmt numFmtId="204" formatCode="0"/>
     <x:numFmt numFmtId="205" formatCode="0.0%"/>
+    <x:numFmt numFmtId="206" formatCode="#,##0"/>
   </x:numFmts>
   <x:fonts count="3">
     <x:font>
@@ -198,7 +244,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -215,6 +261,8 @@
     </x:xf>
     <x:xf numFmtId="204" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="205" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="206" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1096,7 +1144,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb88f286bf3b54ffd"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb30f41bbf554af8"/>
 </x:worksheet>
 </file>
 
@@ -1505,20 +1553,23 @@
       <x:c r="A32" s="1" t="str">
         <x:v>Inductor, chosen</x:v>
       </x:c>
-      <x:c r="B32" s="4"/>
+      <x:c r="B32" s="4" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
       <x:c r="C32" s="1" t="str">
         <x:v>uH</x:v>
       </x:c>
       <x:c r="D32" s="1" t="str">
-        <x:v>TBD; check IC range, tolerance and DC bias</x:v>
+        <x:v>Proposed CYA1265; not yet placed</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="22" customHeight="1">
       <x:c r="A33" s="1" t="str">
         <x:v>Ripple with chosen inductor</x:v>
       </x:c>
-      <x:c r="B33" s="4" t="str">
+      <x:c r="B33" s="4" t="n">
         <x:f>IF(AND(ISNUMBER(B32),B32&gt;0),B6*(1-B6/B5)/(B32*1E-6*B10),"")</x:f>
+        <x:v>2.2847522847522854</x:v>
       </x:c>
       <x:c r="C33" s="1" t="str">
         <x:v>A p-p</x:v>
@@ -1531,8 +1582,9 @@
       <x:c r="A34" s="1" t="str">
         <x:v>Inductor peak current</x:v>
       </x:c>
-      <x:c r="B34" s="4" t="str">
+      <x:c r="B34" s="4" t="n">
         <x:f>IF(ISNUMBER(B33),B9+B33/2,"")</x:f>
+        <x:v>8.142376142376143</x:v>
       </x:c>
       <x:c r="C34" s="1" t="str">
         <x:v>A</x:v>
@@ -1545,8 +1597,9 @@
       <x:c r="A35" s="1" t="str">
         <x:v>Inductor RMS current</x:v>
       </x:c>
-      <x:c r="B35" s="4" t="str">
+      <x:c r="B35" s="4" t="n">
         <x:f>IF(ISNUMBER(B33),SQRT(B9^2+B33^2/12),"")</x:f>
+        <x:v>7.0310033245777515</x:v>
       </x:c>
       <x:c r="C35" s="1" t="str">
         <x:v>A</x:v>
@@ -1677,20 +1730,23 @@
       <x:c r="A46" s="1" t="str">
         <x:v>R bottom, chosen</x:v>
       </x:c>
-      <x:c r="B46" s="4"/>
+      <x:c r="B46" s="13" t="n">
+        <x:v>10000</x:v>
+      </x:c>
       <x:c r="C46" s="1" t="str">
         <x:v>ohm</x:v>
       </x:c>
       <x:c r="D46" s="1" t="str">
-        <x:v>FB to ground</x:v>
+        <x:v>R8</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="22" customHeight="1">
       <x:c r="A47" s="1" t="str">
         <x:v>R top, calculated</x:v>
       </x:c>
-      <x:c r="B47" s="4" t="str">
+      <x:c r="B47" s="13" t="n">
         <x:f>IF(ISNUMBER(B46),B46*(B6/B21-1),"")</x:f>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="C47" s="1" t="str">
         <x:v>ohm</x:v>
@@ -1703,20 +1759,24 @@
       <x:c r="A48" s="1" t="str">
         <x:v>R top, chosen</x:v>
       </x:c>
-      <x:c r="B48" s="4"/>
+      <x:c r="B48" s="13" t="n">
+        <x:f>39000+1000</x:f>
+        <x:v>40000</x:v>
+      </x:c>
       <x:c r="C48" s="1" t="str">
         <x:v>ohm</x:v>
       </x:c>
       <x:c r="D48" s="1" t="str">
-        <x:v>TBD</x:v>
+        <x:v>R9 + R10</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="22" customHeight="1">
       <x:c r="A49" s="1" t="str">
         <x:v>Output with chosen divider</x:v>
       </x:c>
-      <x:c r="B49" s="4" t="str">
+      <x:c r="B49" s="4" t="n">
         <x:f>IF(AND(COUNT(B46,B48)=2,B46&gt;0),B21*(1+B48/B46),"")</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C49" s="1" t="str">
         <x:v>V</x:v>
@@ -1729,36 +1789,42 @@
       <x:c r="A50" s="1" t="str">
         <x:v>Output capacitance, nominal</x:v>
       </x:c>
-      <x:c r="B50" s="4"/>
+      <x:c r="B50" s="4" t="n">
+        <x:f>B77*B79</x:f>
+        <x:v>160</x:v>
+      </x:c>
       <x:c r="C50" s="1" t="str">
         <x:v>uF</x:v>
       </x:c>
       <x:c r="D50" s="1" t="str">
-        <x:v>TBD; bank total</x:v>
+        <x:v>C14-C29</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="22" customHeight="1">
       <x:c r="A51" s="1" t="str">
-        <x:v>Capacitance retained</x:v>
-      </x:c>
-      <x:c r="B51" s="11"/>
+        <x:v>Capacitance retained at 5 V</x:v>
+      </x:c>
+      <x:c r="B51" s="11" t="n">
+        <x:v>0.939267355161395</x:v>
+      </x:c>
       <x:c r="C51" s="1" t="str"/>
       <x:c r="D51" s="1" t="str">
-        <x:v>From DC bias, tolerance and temperature</x:v>
+        <x:v>Typical DC bias only; update if Vout changes</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="22" customHeight="1">
       <x:c r="A52" s="1" t="str">
-        <x:v>Output capacitance, effective</x:v>
-      </x:c>
-      <x:c r="B52" s="4" t="str">
+        <x:v>Output capacitance, typical</x:v>
+      </x:c>
+      <x:c r="B52" s="4" t="n">
         <x:f>IF(COUNT(B50:B51)=2,B50*B51,"")</x:f>
+        <x:v>150.2827768258232</x:v>
       </x:c>
       <x:c r="C52" s="1" t="str">
         <x:v>uF</x:v>
       </x:c>
       <x:c r="D52" s="1" t="str">
-        <x:v>Must also satisfy IC stability / transient needs</x:v>
+        <x:v>Excludes tolerance, temperature and aging</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="22" customHeight="1">
@@ -1770,7 +1836,7 @@
         <x:v>ohm</x:v>
       </x:c>
       <x:c r="D53" s="1" t="str">
-        <x:v>At switching frequency</x:v>
+        <x:v>Unknown; frequency-dependent</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="22" customHeight="1">
@@ -1791,20 +1857,24 @@
       <x:c r="A55" s="1" t="str">
         <x:v>Inductor part</x:v>
       </x:c>
-      <x:c r="B55" s="4"/>
+      <x:c r="B55" s="4" t="str">
+        <x:v>C19268665</x:v>
+      </x:c>
       <x:c r="C55" s="1" t="str"/>
       <x:c r="D55" s="1" t="str">
-        <x:v>TBD</x:v>
+        <x:v>CYA1265-3.3UH (proposed)</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="22" customHeight="1">
       <x:c r="A56" s="1" t="str">
-        <x:v>Output capacitor part</x:v>
-      </x:c>
-      <x:c r="B56" s="4"/>
+        <x:v>Capacitor part</x:v>
+      </x:c>
+      <x:c r="B56" s="4" t="str">
+        <x:v>C138687</x:v>
+      </x:c>
       <x:c r="C56" s="1" t="str"/>
       <x:c r="D56" s="1" t="str">
-        <x:v>TBD; keep DC-bias curve beside this calculation</x:v>
+        <x:v>CL32B106KBJNNNE, 50 V X7R</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="22" customHeight="1">
@@ -1814,16 +1884,477 @@
       <x:c r="D57" s="1"/>
     </x:row>
     <x:row r="58" ht="22" customHeight="1">
-      <x:c r="A58" s="1"/>
-      <x:c r="B58" s="1"/>
-      <x:c r="C58" s="1"/>
-      <x:c r="D58" s="1"/>
+      <x:c r="A58" s="8" t="str">
+        <x:v>Loop compensation / feed-forward</x:v>
+      </x:c>
+      <x:c r="B58" s="9"/>
+      <x:c r="C58" s="8"/>
+      <x:c r="D58" s="8"/>
     </x:row>
     <x:row r="59" ht="22" customHeight="1">
-      <x:c r="A59" s="1"/>
-      <x:c r="B59" s="1"/>
-      <x:c r="C59" s="1"/>
-      <x:c r="D59" s="1"/>
+      <x:c r="A59" s="1" t="str">
+        <x:v>Parameter</x:v>
+      </x:c>
+      <x:c r="B59" s="4" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="str">
+        <x:v>Note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="1" t="str">
+        <x:v>RFF, proposed</x:v>
+      </x:c>
+      <x:c r="B60" s="13" t="n">
+        <x:v>4990</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="str">
+        <x:v>Series with CFF, across the full R9 + R10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="22" customHeight="1">
+      <x:c r="A61" s="1" t="str">
+        <x:v>CFF, proposed</x:v>
+      </x:c>
+      <x:c r="B61" s="13" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="str">
+        <x:v>pF</x:v>
+      </x:c>
+      <x:c r="D61" s="1" t="str">
+        <x:v>C0G/NP0; starting value, not yet placed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="22" customHeight="1">
+      <x:c r="A62" s="1" t="str">
+        <x:v>R top || R bottom</x:v>
+      </x:c>
+      <x:c r="B62" s="4" t="n">
+        <x:f>B48*B46/(B48+B46)</x:f>
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="D62" s="1" t="str"/>
+    </x:row>
+    <x:row r="63" ht="22" customHeight="1">
+      <x:c r="A63" s="1" t="str">
+        <x:v>Feed-forward zero</x:v>
+      </x:c>
+      <x:c r="B63" s="4" t="n">
+        <x:f>IF(AND(ISNUMBER(B61),B61&gt;0),1/(2*PI()*(B48+B60)*B61*1E-12)/1000,"")</x:f>
+        <x:v>107.19886782375568</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="str">
+        <x:v>kHz</x:v>
+      </x:c>
+      <x:c r="D63" s="1" t="str">
+        <x:v>1 / [2pi (Rtop + RFF) CFF]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="1" t="str">
+        <x:v>Feed-forward pole</x:v>
+      </x:c>
+      <x:c r="B64" s="4" t="n">
+        <x:f>IF(AND(ISNUMBER(B61),B61&gt;0),1/(2*PI()*(B62+B60)*B61*1E-12)/1000,"")</x:f>
+        <x:v>371.27614036880425</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="str">
+        <x:v>kHz</x:v>
+      </x:c>
+      <x:c r="D64" s="1" t="str">
+        <x:v>1 / [2pi (Rtop || Rbottom + RFF) CFF]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="1" t="str">
+        <x:v>ESR at capacitor zero</x:v>
+      </x:c>
+      <x:c r="B65" s="4"/>
+      <x:c r="C65" s="1" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="str">
+        <x:v>Requires bank impedance near its zero</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="22" customHeight="1">
+      <x:c r="A66" s="1" t="str">
+        <x:v>Capacitor ESR zero</x:v>
+      </x:c>
+      <x:c r="B66" s="4" t="str">
+        <x:f>IF(AND(ISNUMBER(B65),B65&gt;0,B52&gt;0),1/(2*PI()*B65*B52*1E-6)/1000,"")</x:f>
+      </x:c>
+      <x:c r="C66" s="1" t="str">
+        <x:v>kHz</x:v>
+      </x:c>
+      <x:c r="D66" s="1" t="str">
+        <x:v>Single-ESR bank approximation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="22" customHeight="1">
+      <x:c r="A67" s="1" t="str">
+        <x:v>TI ESR-zero boundary</x:v>
+      </x:c>
+      <x:c r="B67" s="4" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="str">
+        <x:v>kHz</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="str">
+        <x:v>Below this: omit CFF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="22" customHeight="1">
+      <x:c r="A68" s="1" t="str">
+        <x:v>ESR at boundary</x:v>
+      </x:c>
+      <x:c r="B68" s="4" t="n">
+        <x:f>1/(2*PI()*B67*1000*B52*1E-6)*1000</x:f>
+        <x:v>5.295182403914286</x:v>
+      </x:c>
+      <x:c r="C68" s="1" t="str">
+        <x:v>mohm</x:v>
+      </x:c>
+      <x:c r="D68" s="1" t="str">
+        <x:v>Based on typical output capacitance</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="22" customHeight="1">
+      <x:c r="A69" s="1" t="str">
+        <x:v>CFF condition</x:v>
+      </x:c>
+      <x:c r="B69" s="4" t="str">
+        <x:f>IF(ISNUMBER(B66),IF(B66&lt;B67,"Omit CFF","Tune CFF"),"ESR needed")</x:f>
+        <x:v>ESR needed</x:v>
+      </x:c>
+      <x:c r="C69" s="1" t="str"/>
+      <x:c r="D69" s="1" t="str">
+        <x:v>RC zero/pole do not give loop phase margin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="22" customHeight="1">
+      <x:c r="A70" s="1" t="str">
+        <x:v>Loop stability</x:v>
+      </x:c>
+      <x:c r="B70" s="4" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="C70" s="1" t="str"/>
+      <x:c r="D70" s="1" t="str">
+        <x:v>Internal compensation; verify full loop and transients</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="22" customHeight="1">
+      <x:c r="A71" s="1" t="str">
+        <x:v>TI example CFF</x:v>
+      </x:c>
+      <x:c r="B71" s="13" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C71" s="1" t="str">
+        <x:v>pF</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="str">
+        <x:v>100k / 24.9k divider, Table 9-3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="22" customHeight="1">
+      <x:c r="A72" s="1" t="str">
+        <x:v>TI example R top</x:v>
+      </x:c>
+      <x:c r="B72" s="13" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="C72" s="1" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="D72" s="1" t="str"/>
+    </x:row>
+    <x:row r="73" ht="22" customHeight="1">
+      <x:c r="A73" s="1" t="str">
+        <x:v>CFF for same zero</x:v>
+      </x:c>
+      <x:c r="B73" s="4" t="n">
+        <x:f>(B72+B60)*B71/(B48+B60)</x:f>
+        <x:v>35.00444543231829</x:v>
+      </x:c>
+      <x:c r="C73" s="1" t="str">
+        <x:v>pF</x:v>
+      </x:c>
+      <x:c r="D73" s="1" t="str">
+        <x:v>Frequency scaling only, not a stability calculation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="22" customHeight="1">
+      <x:c r="A74" s="1"/>
+      <x:c r="B74" s="4"/>
+      <x:c r="C74" s="1"/>
+      <x:c r="D74" s="1"/>
+    </x:row>
+    <x:row r="75" ht="22" customHeight="1">
+      <x:c r="A75" s="8" t="str">
+        <x:v>Capacitor banks</x:v>
+      </x:c>
+      <x:c r="B75" s="9"/>
+      <x:c r="C75" s="8"/>
+      <x:c r="D75" s="8"/>
+    </x:row>
+    <x:row r="76" ht="22" customHeight="1">
+      <x:c r="A76" s="1" t="str">
+        <x:v>Parameter</x:v>
+      </x:c>
+      <x:c r="B76" s="4" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C76" s="1" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="D76" s="1" t="str">
+        <x:v>Note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="22" customHeight="1">
+      <x:c r="A77" s="1" t="str">
+        <x:v>Capacitance per part</x:v>
+      </x:c>
+      <x:c r="B77" s="13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C77" s="1" t="str">
+        <x:v>uF</x:v>
+      </x:c>
+      <x:c r="D77" s="1" t="str">
+        <x:v>C138687</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="22" customHeight="1">
+      <x:c r="A78" s="1" t="str">
+        <x:v>Input capacitor count</x:v>
+      </x:c>
+      <x:c r="B78" s="13" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C78" s="1" t="str"/>
+      <x:c r="D78" s="1" t="str">
+        <x:v>C10-C13; 100 nF bypasses excluded</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="22" customHeight="1">
+      <x:c r="A79" s="1" t="str">
+        <x:v>Output capacitor count</x:v>
+      </x:c>
+      <x:c r="B79" s="13" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C79" s="1" t="str"/>
+      <x:c r="D79" s="1" t="str">
+        <x:v>C14-C29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="22" customHeight="1">
+      <x:c r="A80" s="1" t="str">
+        <x:v>Input retained at 12.6 V</x:v>
+      </x:c>
+      <x:c r="B80" s="11" t="n">
+        <x:v>0.7239619908473031</x:v>
+      </x:c>
+      <x:c r="C80" s="1" t="str"/>
+      <x:c r="D80" s="1" t="str">
+        <x:v>Typical DC bias only; update if Vin changes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="22" customHeight="1">
+      <x:c r="A81" s="1" t="str">
+        <x:v>Input capacitance, nominal</x:v>
+      </x:c>
+      <x:c r="B81" s="4" t="n">
+        <x:f>B77*B78</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C81" s="1" t="str">
+        <x:v>uF</x:v>
+      </x:c>
+      <x:c r="D81" s="1" t="str"/>
+    </x:row>
+    <x:row r="82" ht="22" customHeight="1">
+      <x:c r="A82" s="1" t="str">
+        <x:v>Input capacitance, typical</x:v>
+      </x:c>
+      <x:c r="B82" s="4" t="n">
+        <x:f>B81*B80</x:f>
+        <x:v>28.95847963389212</x:v>
+      </x:c>
+      <x:c r="C82" s="1" t="str">
+        <x:v>uF</x:v>
+      </x:c>
+      <x:c r="D82" s="1" t="str">
+        <x:v>Excludes tolerance, temperature and aging</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="22" customHeight="1">
+      <x:c r="A83" s="1" t="str">
+        <x:v>Capacitive output ripple</x:v>
+      </x:c>
+      <x:c r="B83" s="4" t="n">
+        <x:f>B33/(8*B10*B52*1E-6)*1000</x:f>
+        <x:v>4.750944213737769</x:v>
+      </x:c>
+      <x:c r="C83" s="1" t="str">
+        <x:v>mV p-p</x:v>
+      </x:c>
+      <x:c r="D83" s="1" t="str">
+        <x:v>CCM estimate; excludes ESR, ESL and transients</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="22" customHeight="1">
+      <x:c r="A84" s="1"/>
+      <x:c r="B84" s="4"/>
+      <x:c r="C84" s="1"/>
+      <x:c r="D84" s="1"/>
+    </x:row>
+    <x:row r="85" ht="22" customHeight="1">
+      <x:c r="A85" s="8" t="str">
+        <x:v>Inductor limits</x:v>
+      </x:c>
+      <x:c r="B85" s="9"/>
+      <x:c r="C85" s="8"/>
+      <x:c r="D85" s="8"/>
+    </x:row>
+    <x:row r="86" ht="22" customHeight="1">
+      <x:c r="A86" s="1" t="str">
+        <x:v>Parameter</x:v>
+      </x:c>
+      <x:c r="B86" s="4" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C86" s="1" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="D86" s="1" t="str">
+        <x:v>Note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="22" customHeight="1">
+      <x:c r="A87" s="1" t="str">
+        <x:v>Minimum frequency</x:v>
+      </x:c>
+      <x:c r="B87" s="13" t="n">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="C87" s="1" t="str">
+        <x:v>Hz</x:v>
+      </x:c>
+      <x:c r="D87" s="1" t="str">
+        <x:v>RT = VCC, spread spectrum off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="22" customHeight="1">
+      <x:c r="A88" s="1" t="str">
+        <x:v>Inductance tolerance</x:v>
+      </x:c>
+      <x:c r="B88" s="11" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="C88" s="1" t="str"/>
+      <x:c r="D88" s="1" t="str">
+        <x:v>Before DC bias and temperature</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="22" customHeight="1">
+      <x:c r="A89" s="1" t="str">
+        <x:v>Inductance, initial minimum</x:v>
+      </x:c>
+      <x:c r="B89" s="4" t="n">
+        <x:f>B32*(1-B88)</x:f>
+        <x:v>2.64</x:v>
+      </x:c>
+      <x:c r="C89" s="1" t="str">
+        <x:v>uH</x:v>
+      </x:c>
+      <x:c r="D89" s="1" t="str"/>
+    </x:row>
+    <x:row r="90" ht="22" customHeight="1">
+      <x:c r="A90" s="1" t="str">
+        <x:v>TI minimum inductance</x:v>
+      </x:c>
+      <x:c r="B90" s="4" t="n">
+        <x:f>B6/(B87*0.6*B19)*1E6</x:f>
+        <x:v>2.380952380952381</x:v>
+      </x:c>
+      <x:c r="C90" s="1" t="str">
+        <x:v>uH</x:v>
+      </x:c>
+      <x:c r="D90" s="1" t="str">
+        <x:v>Equation 6; use operating inductance</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="22" customHeight="1">
+      <x:c r="A91" s="1" t="str">
+        <x:v>Required retention in use</x:v>
+      </x:c>
+      <x:c r="B91" s="11" t="n">
+        <x:f>B90/B89</x:f>
+        <x:v>0.9018759018759018</x:v>
+      </x:c>
+      <x:c r="C91" s="1" t="str"/>
+      <x:c r="D91" s="1" t="str">
+        <x:v>L-versus-current/temperature curve still needed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="22" customHeight="1">
+      <x:c r="A92" s="1" t="str">
+        <x:v>Inductor DCR, maximum</x:v>
+      </x:c>
+      <x:c r="B92" s="4" t="n">
+        <x:v>6.5</x:v>
+      </x:c>
+      <x:c r="C92" s="1" t="str">
+        <x:v>mohm</x:v>
+      </x:c>
+      <x:c r="D92" s="1" t="str">
+        <x:v>At 25 C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="22" customHeight="1">
+      <x:c r="A93" s="1" t="str">
+        <x:v>Inductor copper loss</x:v>
+      </x:c>
+      <x:c r="B93" s="4" t="n">
+        <x:f>B35^2*B92/1000</x:f>
+        <x:v>0.32132755037645205</x:v>
+      </x:c>
+      <x:c r="C93" s="1" t="str">
+        <x:v>W</x:v>
+      </x:c>
+      <x:c r="D93" s="1" t="str">
+        <x:v>At design load; excludes core, AC and hot DCR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="22" customHeight="1">
+      <x:c r="A94" s="1" t="str">
+        <x:v>Saturation current</x:v>
+      </x:c>
+      <x:c r="B94" s="4" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C94" s="1" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="D94" s="1" t="str">
+        <x:v>30% L drop; thermal rating 25 A at 40 C rise</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1831,9 +2362,12 @@
     <x:mergeCell ref="A17:D17"/>
     <x:mergeCell ref="A24:D24"/>
     <x:mergeCell ref="A44:D44"/>
+    <x:mergeCell ref="A58:D58"/>
+    <x:mergeCell ref="A75:D75"/>
+    <x:mergeCell ref="A85:D85"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4c649af2de247a5"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e7e1c5a67074b4e"/>
 </x:worksheet>
 </file>
 
@@ -2570,7 +3104,7 @@
     <x:mergeCell ref="A44:D44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d582a5b7d2145c0"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7815574824b4c42"/>
 </x:worksheet>
 </file>
 
@@ -3163,7 +3697,7 @@
     <x:mergeCell ref="A33:D33"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69b16face3c14bc4"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87b36ebf19ef4f21"/>
 </x:worksheet>
 </file>
 
@@ -3756,7 +4290,7 @@
     <x:mergeCell ref="A33:D33"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8a4056d625840d3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42b20e13471c4b63"/>
 </x:worksheet>
 </file>
 
@@ -3767,7 +4301,7 @@
     <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="9" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="47" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="63" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -4092,24 +4626,284 @@
       <x:c r="D29" s="1"/>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="1"/>
-      <x:c r="B30" s="1"/>
-      <x:c r="C30" s="1"/>
-      <x:c r="D30" s="1"/>
+      <x:c r="A30" s="8" t="str">
+        <x:v>Input protection and current sense</x:v>
+      </x:c>
+      <x:c r="B30" s="9"/>
+      <x:c r="C30" s="8"/>
+      <x:c r="D30" s="8"/>
     </x:row>
     <x:row r="31" ht="22" customHeight="1">
-      <x:c r="A31" s="1"/>
-      <x:c r="B31" s="1"/>
-      <x:c r="C31" s="1"/>
-      <x:c r="D31" s="1"/>
+      <x:c r="A31" s="1" t="str">
+        <x:v>Parameter</x:v>
+      </x:c>
+      <x:c r="B31" s="4" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="str">
+        <x:v>Note</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="1"/>
-      <x:c r="B32" s="1"/>
-      <x:c r="C32" s="1"/>
-      <x:c r="D32" s="1"/>
+      <x:c r="A32" s="1" t="str">
+        <x:v>UVLO top / bottom</x:v>
+      </x:c>
+      <x:c r="B32" s="4" t="n">
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="str">
+        <x:v>R1; bottom R2 below</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
+      <x:c r="A33" s="1" t="str">
+        <x:v>UVLO bottom</x:v>
+      </x:c>
+      <x:c r="B33" s="4" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="str">
+        <x:v>R2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
+      <x:c r="A34" s="1" t="str">
+        <x:v>UVLO falling threshold</x:v>
+      </x:c>
+      <x:c r="B34" s="4" t="n">
+        <x:v>1.14</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="str">
+        <x:v>V</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="str">
+        <x:v>LM74502 nominal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="22" customHeight="1">
+      <x:c r="A35" s="1" t="str">
+        <x:v>UVLO rising threshold</x:v>
+      </x:c>
+      <x:c r="B35" s="4" t="n">
+        <x:v>1.24</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="str">
+        <x:v>V</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="str">
+        <x:v>LM74502 nominal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="22" customHeight="1">
+      <x:c r="A36" s="1" t="str">
+        <x:v>Battery turn-off</x:v>
+      </x:c>
+      <x:c r="B36" s="4" t="n">
+        <x:f>B34*(1+B32/B33)</x:f>
+        <x:v>9.69</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="str">
+        <x:v>V</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="str">
+        <x:v>Nominal; excludes bias and tolerances</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
+      <x:c r="A37" s="1" t="str">
+        <x:v>Battery turn-on</x:v>
+      </x:c>
+      <x:c r="B37" s="4" t="n">
+        <x:f>B35*(1+B32/B33)</x:f>
+        <x:v>10.54</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="str">
+        <x:v>V</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="str"/>
+    </x:row>
+    <x:row r="38" ht="22" customHeight="1">
+      <x:c r="A38" s="1" t="str">
+        <x:v>OV top</x:v>
+      </x:c>
+      <x:c r="B38" s="4" t="n">
+        <x:v>51000</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="str">
+        <x:v>R3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="22" customHeight="1">
+      <x:c r="A39" s="1" t="str">
+        <x:v>OV bottom</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="n">
+        <x:v>4700</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="str">
+        <x:v>R4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="22" customHeight="1">
+      <x:c r="A40" s="1" t="str">
+        <x:v>OV rising threshold</x:v>
+      </x:c>
+      <x:c r="B40" s="4" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="str">
+        <x:v>V</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="str">
+        <x:v>LM74502 nominal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="22" customHeight="1">
+      <x:c r="A41" s="1" t="str">
+        <x:v>Overvoltage trip</x:v>
+      </x:c>
+      <x:c r="B41" s="4" t="n">
+        <x:f>B40*(1+B38/B39)</x:f>
+        <x:v>14.813829787234043</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="str">
+        <x:v>V</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="str">
+        <x:v>Nominal; excludes bias and tolerances</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="22" customHeight="1">
+      <x:c r="A42" s="1" t="str">
+        <x:v>VCAP</x:v>
+      </x:c>
+      <x:c r="B42" s="4" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="str">
+        <x:v>nF</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="str">
+        <x:v>C2, CAP to VS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="22" customHeight="1">
+      <x:c r="A43" s="1" t="str">
+        <x:v>Battery bulk</x:v>
+      </x:c>
+      <x:c r="B43" s="4" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="str">
+        <x:v>uF</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="str">
+        <x:v>C9, EEEFK1V221P, 35 V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="22" customHeight="1">
+      <x:c r="A44" s="1" t="str">
+        <x:v>Shunt resistance</x:v>
+      </x:c>
+      <x:c r="B44" s="4" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="str">
+        <x:v>R6, WSL25125L000FEA18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="22" customHeight="1">
+      <x:c r="A45" s="1" t="str">
+        <x:v>Shunt voltage at design load</x:v>
+      </x:c>
+      <x:c r="B45" s="4" t="n">
+        <x:f>B27*B44*1000</x:f>
+        <x:v>25.66255144032922</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="str">
+        <x:v>mV</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="str"/>
+    </x:row>
+    <x:row r="46" ht="22" customHeight="1">
+      <x:c r="A46" s="1" t="str">
+        <x:v>Shunt dissipation</x:v>
+      </x:c>
+      <x:c r="B46" s="4" t="n">
+        <x:f>B27^2*B44</x:f>
+        <x:v>0.13171330928550867</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="str">
+        <x:v>W</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="str">
+        <x:v>At design battery current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="22" customHeight="1">
+      <x:c r="A47" s="1" t="str">
+        <x:v>Filter resistance, per input</x:v>
+      </x:c>
+      <x:c r="B47" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="str">
+        <x:v>R5 and R7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="22" customHeight="1">
+      <x:c r="A48" s="1" t="str">
+        <x:v>Differential filter capacitor</x:v>
+      </x:c>
+      <x:c r="B48" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="str">
+        <x:v>uF</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="str">
+        <x:v>C8, between sense inputs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="22" customHeight="1">
+      <x:c r="A49" s="1" t="str">
+        <x:v>Differential filter pole</x:v>
+      </x:c>
+      <x:c r="B49" s="4" t="n">
+        <x:f>1/(2*PI()*2*B47*B48*1E-6)/1000</x:f>
+        <x:v>7.9577471545947684</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="str">
+        <x:v>kHz</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="str"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A30:D30"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30236a20a8ac44dd"/>
 </x:worksheet>
 </file>